--- a/web/files/港岛-薄扶林-Victoria Coast.xlsx
+++ b/web/files/港岛-薄扶林-Victoria Coast.xlsx
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -122,6 +122,12 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
       <color rgb="00660000"/>
       <sz val="8"/>
     </font>
@@ -196,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -258,7 +264,10 @@
     <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -750,7 +759,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -760,12 +769,12 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -775,12 +784,12 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
@@ -790,7 +799,7 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -8986,27 +8995,27 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>40</t>
         </is>
       </c>
     </row>
@@ -9041,12 +9050,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr">
+      <c r="C5" s="21" t="inlineStr">
         <is>
           <t>2 | 1367呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>
@@ -9087,7 +9096,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>2 | 1367呎 (3房)
 $3120万
@@ -9156,7 +9165,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C10" s="21" t="inlineStr">
+      <c r="C10" s="22" t="inlineStr">
         <is>
           <t>2 | 1367呎 (3房)
 $3210万
@@ -9271,7 +9280,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C15" s="21" t="inlineStr">
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t>2 | 1367呎 (3房)
 $3481万
@@ -9294,7 +9303,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C16" s="21" t="inlineStr">
+      <c r="C16" s="22" t="inlineStr">
         <is>
           <t>2 | 1367呎 (3房)
 $3050万
@@ -9317,7 +9326,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C17" s="21" t="inlineStr">
+      <c r="C17" s="22" t="inlineStr">
         <is>
           <t>2 | 1367呎 (3房)
 $3363万
@@ -9363,7 +9372,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C19" s="21" t="inlineStr">
+      <c r="C19" s="22" t="inlineStr">
         <is>
           <t>2 | 1367呎 (3房)
 $3000万
@@ -9378,7 +9387,7 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B20" s="21" t="inlineStr">
+      <c r="B20" s="22" t="inlineStr">
         <is>
           <t>1 | 1363呎 (3房)
 $2780万
@@ -9432,7 +9441,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C22" s="21" t="inlineStr">
+      <c r="C22" s="22" t="inlineStr">
         <is>
           <t>2 | 1367呎 (2房)
 $2550万
@@ -9501,7 +9510,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C25" s="21" t="inlineStr">
+      <c r="C25" s="22" t="inlineStr">
         <is>
           <t>2 | 1367呎 (2房)
 $2750万
@@ -9524,7 +9533,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C26" s="21" t="inlineStr">
+      <c r="C26" s="22" t="inlineStr">
         <is>
           <t>2 | 1367呎 (2房)
 $2650万
@@ -9616,7 +9625,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C30" s="21" t="inlineStr">
+      <c r="C30" s="22" t="inlineStr">
         <is>
           <t>2 | 1367呎 (2房)
 $2500万
@@ -9631,7 +9640,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="B31" s="21" t="inlineStr">
+      <c r="B31" s="22" t="inlineStr">
         <is>
           <t>1 | 1363呎 (2房)
 $2426万
@@ -9639,7 +9648,7 @@
 (24年-05月-21日)</t>
         </is>
       </c>
-      <c r="C31" s="21" t="inlineStr">
+      <c r="C31" s="22" t="inlineStr">
         <is>
           <t>2 | 1367呎 (2房)
 $2360万
@@ -9654,7 +9663,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B32" s="21" t="inlineStr">
+      <c r="B32" s="22" t="inlineStr">
         <is>
           <t>1 | 1363呎 (2房)
 $2605万
@@ -9662,7 +9671,7 @@
 (23年-10月-27日)</t>
         </is>
       </c>
-      <c r="C32" s="21" t="inlineStr">
+      <c r="C32" s="22" t="inlineStr">
         <is>
           <t>2 | 1367呎 (2房)
 $2310万
@@ -9677,7 +9686,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B33" s="21" t="inlineStr">
+      <c r="B33" s="22" t="inlineStr">
         <is>
           <t>1 | 1363呎 (2房)
 $2481万
@@ -9685,7 +9694,7 @@
 (23年-10月-19日)</t>
         </is>
       </c>
-      <c r="C33" s="21" t="inlineStr">
+      <c r="C33" s="22" t="inlineStr">
         <is>
           <t>2 | 1367呎 (2房)
 $2206万

--- a/web/files/港岛-薄扶林-Victoria Coast.xlsx
+++ b/web/files/港岛-薄扶林-Victoria Coast.xlsx
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -122,12 +122,6 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
       <color rgb="00660000"/>
       <sz val="8"/>
     </font>
@@ -202,7 +196,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -264,10 +258,7 @@
     <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -759,23 +750,19 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>36000000</v>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>26335</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -784,12 +771,12 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
@@ -799,7 +786,7 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -8995,7 +8982,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -9005,7 +8992,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -9053,9 +9040,9 @@
       <c r="C5" s="21" t="inlineStr">
         <is>
           <t>2 | 1367呎 (3房)
-招标单位
--
-(在售)</t>
+$3600万
+$26,335/呎
+(26年-09月-12日)</t>
         </is>
       </c>
     </row>
@@ -9096,7 +9083,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>2 | 1367呎 (3房)
 $3120万
@@ -9165,7 +9152,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C10" s="22" t="inlineStr">
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>2 | 1367呎 (3房)
 $3210万
@@ -9280,7 +9267,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C15" s="22" t="inlineStr">
+      <c r="C15" s="21" t="inlineStr">
         <is>
           <t>2 | 1367呎 (3房)
 $3481万
@@ -9303,7 +9290,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C16" s="22" t="inlineStr">
+      <c r="C16" s="21" t="inlineStr">
         <is>
           <t>2 | 1367呎 (3房)
 $3050万
@@ -9326,7 +9313,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C17" s="22" t="inlineStr">
+      <c r="C17" s="21" t="inlineStr">
         <is>
           <t>2 | 1367呎 (3房)
 $3363万
@@ -9372,7 +9359,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C19" s="22" t="inlineStr">
+      <c r="C19" s="21" t="inlineStr">
         <is>
           <t>2 | 1367呎 (3房)
 $3000万
@@ -9387,7 +9374,7 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B20" s="22" t="inlineStr">
+      <c r="B20" s="21" t="inlineStr">
         <is>
           <t>1 | 1363呎 (3房)
 $2780万
@@ -9441,7 +9428,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C22" s="22" t="inlineStr">
+      <c r="C22" s="21" t="inlineStr">
         <is>
           <t>2 | 1367呎 (2房)
 $2550万
@@ -9510,7 +9497,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C25" s="22" t="inlineStr">
+      <c r="C25" s="21" t="inlineStr">
         <is>
           <t>2 | 1367呎 (2房)
 $2750万
@@ -9533,7 +9520,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C26" s="22" t="inlineStr">
+      <c r="C26" s="21" t="inlineStr">
         <is>
           <t>2 | 1367呎 (2房)
 $2650万
@@ -9625,7 +9612,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C30" s="22" t="inlineStr">
+      <c r="C30" s="21" t="inlineStr">
         <is>
           <t>2 | 1367呎 (2房)
 $2500万
@@ -9640,7 +9627,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="B31" s="22" t="inlineStr">
+      <c r="B31" s="21" t="inlineStr">
         <is>
           <t>1 | 1363呎 (2房)
 $2426万
@@ -9648,7 +9635,7 @@
 (24年-05月-21日)</t>
         </is>
       </c>
-      <c r="C31" s="22" t="inlineStr">
+      <c r="C31" s="21" t="inlineStr">
         <is>
           <t>2 | 1367呎 (2房)
 $2360万
@@ -9663,7 +9650,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B32" s="22" t="inlineStr">
+      <c r="B32" s="21" t="inlineStr">
         <is>
           <t>1 | 1363呎 (2房)
 $2605万
@@ -9671,7 +9658,7 @@
 (23年-10月-27日)</t>
         </is>
       </c>
-      <c r="C32" s="22" t="inlineStr">
+      <c r="C32" s="21" t="inlineStr">
         <is>
           <t>2 | 1367呎 (2房)
 $2310万
@@ -9686,7 +9673,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B33" s="22" t="inlineStr">
+      <c r="B33" s="21" t="inlineStr">
         <is>
           <t>1 | 1363呎 (2房)
 $2481万
@@ -9694,7 +9681,7 @@
 (23年-10月-19日)</t>
         </is>
       </c>
-      <c r="C33" s="22" t="inlineStr">
+      <c r="C33" s="21" t="inlineStr">
         <is>
           <t>2 | 1367呎 (2房)
 $2206万

--- a/web/files/港岛-薄扶林-Victoria Coast.xlsx
+++ b/web/files/港岛-薄扶林-Victoria Coast.xlsx
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -125,6 +125,12 @@
       <color rgb="00660000"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -196,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -259,6 +265,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2822,7 +2831,7 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
@@ -2832,12 +2841,12 @@
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -2847,12 +2856,12 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
@@ -2862,7 +2871,7 @@
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -8982,27 +8991,27 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
     </row>
@@ -9382,12 +9391,12 @@
 (24年-05月-30日)</t>
         </is>
       </c>
-      <c r="C20" s="20" t="inlineStr">
+      <c r="C20" s="22" t="inlineStr">
         <is>
           <t>2 | 1367呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>

--- a/web/files/港岛-薄扶林-Victoria Coast.xlsx
+++ b/web/files/港岛-薄扶林-Victoria Coast.xlsx
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -125,12 +125,6 @@
       <color rgb="00660000"/>
       <sz val="8"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="8"/>
-    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -202,7 +196,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -265,9 +259,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2831,23 +2822,19 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>29200000</v>
+      </c>
+      <c r="I33" s="5" t="n">
+        <v>21361</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
@@ -2856,12 +2843,12 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
@@ -2871,7 +2858,7 @@
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -8991,7 +8978,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -9001,7 +8988,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -9391,12 +9378,12 @@
 (24年-05月-30日)</t>
         </is>
       </c>
-      <c r="C20" s="22" t="inlineStr">
+      <c r="C20" s="21" t="inlineStr">
         <is>
           <t>2 | 1367呎 (3房)
-招标单位
--
-(在售)</t>
+$2920万
+$21,361/呎
+(26年-09月-27日)</t>
         </is>
       </c>
     </row>

--- a/web/files/港岛-薄扶林-Victoria Coast.xlsx
+++ b/web/files/港岛-薄扶林-Victoria Coast.xlsx
@@ -755,7 +755,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
@@ -9038,7 +9038,7 @@
           <t>2 | 1367呎 (3房)
 $3600万
 $26,335/呎
-(26年-09月-12日)</t>
+(26年-09月-29日)</t>
         </is>
       </c>
     </row>

--- a/web/files/港岛-薄扶林-Victoria Coast.xlsx
+++ b/web/files/港岛-薄扶林-Victoria Coast.xlsx
@@ -2827,7 +2827,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2954,23 +2954,19 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I35" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>27300000</v>
+      </c>
+      <c r="I35" s="5" t="n">
+        <v>19971</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
@@ -8988,7 +8984,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -8998,7 +8994,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>38</t>
         </is>
       </c>
     </row>
@@ -9383,7 +9379,7 @@
           <t>2 | 1367呎 (3房)
 $2920万
 $21,361/呎
-(26年-09月-27日)</t>
+(26年-10月-26日)</t>
         </is>
       </c>
     </row>
@@ -9401,12 +9397,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C21" s="20" t="inlineStr">
+      <c r="C21" s="21" t="inlineStr">
         <is>
           <t>2 | 1367呎 (2房)
--
--
-(待售)</t>
+$2730万
+$19,971/呎
+(26年-10月-27日)</t>
         </is>
       </c>
     </row>
